--- a/artfynd/A 16317-2026 artfynd.xlsx
+++ b/artfynd/A 16317-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96353678</v>
+        <v>96353650</v>
       </c>
       <c r="B2" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87196</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5964</v>
+        <v>427</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,7 +710,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -726,22 +721,22 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>533489.7958834018</v>
+        <v>533418</v>
       </c>
       <c r="R2" t="n">
-        <v>6334126.908102978</v>
+        <v>6334133</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Kronoberg</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Högsby</t>
+          <t>Uppvidinge</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -751,7 +746,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Fagerhult</t>
+          <t>Åseda</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -759,19 +754,9 @@
           <t>2021-09-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,7 +780,1125 @@
           <t>Tobias Ivarsson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>96353629</v>
+      </c>
+      <c r="B3" t="n">
+        <v>87322</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1988</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kryddspindling</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Cortinarius percomis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog S. om Gruvebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>533448</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6334121</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Fagerhult</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>96353699</v>
+      </c>
+      <c r="B4" t="n">
+        <v>87322</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1988</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kryddspindling</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cortinarius percomis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog S. om Gruvebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>533476</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6334110</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Fagerhult</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>96353623</v>
+      </c>
+      <c r="B5" t="n">
+        <v>87375</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3739</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Persiljespindling</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cortinarius sulfurinus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Quél.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog S. om Gruvebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>533448</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6334121</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Fagerhult</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>96353467</v>
+      </c>
+      <c r="B6" t="n">
+        <v>87391</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3767</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Violettfläckig spindling</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cortinarius violaceomaculatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Brandrud</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog S. om Gruvebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>533498</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6334074</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Fagerhult</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>96353693</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog S. om Gruvebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>533476</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6334110</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Fagerhult</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>96353476</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog S. om Gruvebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>533498</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6334074</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Fagerhult</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>96353667</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog S. om Gruvebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>533418</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6334133</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Uppvidinge</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Åseda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>96353678</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog S. om Gruvebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>533489</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6334127</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Fagerhult</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>96353697</v>
+      </c>
+      <c r="B11" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog S. om Gruvebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>533476</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6334110</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Fagerhult</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>96353705</v>
+      </c>
+      <c r="B12" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog S. om Gruvebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>533547</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6334075</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Fagerhult</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tobias Ivarsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
         <is>
           <t>Mykorrhizasvampar i kalkbarrskog och sandbarrskog 2020, Kalkbarrskogsinventering i Kalmar län 2020-2021</t>
         </is>
